--- a/株式会社ワクトリ御中_LINEOA施策提案【SIM】ver1.3.xlsx
+++ b/株式会社ワクトリ御中_LINEOA施策提案【SIM】ver1.3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tonomura-r\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A27D118C-E5AE-48BE-B104-54DFFCAAFE0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A53ED74B-4FDE-4FF6-A2B3-58EF69870AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-13380" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{02433765-3560-48F5-BC99-B30FC64129A4}"/>
+    <workbookView xWindow="-13380" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{02433765-3560-48F5-BC99-B30FC64129A4}"/>
   </bookViews>
   <sheets>
     <sheet name="SIM①_月4投稿" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="SIM②_比較" sheetId="4" r:id="rId4"/>
     <sheet name="SIM考え方" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2541,12 +2541,42 @@
     <xf numFmtId="14" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2568,40 +2598,10 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3052,7 +3052,7 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="137" t="s">
+      <c r="A8" s="147" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="19" t="s">
@@ -3085,7 +3085,7 @@
       </c>
     </row>
     <row r="9" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="138"/>
+      <c r="A9" s="148"/>
       <c r="B9" s="19" t="s">
         <v>8</v>
       </c>
@@ -3115,7 +3115,7 @@
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="137" t="s">
+      <c r="A10" s="147" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="19" t="s">
@@ -3143,7 +3143,7 @@
       </c>
     </row>
     <row r="11" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="138"/>
+      <c r="A11" s="148"/>
       <c r="B11" s="19" t="s">
         <v>11</v>
       </c>
@@ -3177,10 +3177,10 @@
       <c r="V12" s="55"/>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="139" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="139"/>
+      <c r="A13" s="149" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="149"/>
       <c r="C13" s="95"/>
       <c r="D13" s="13" t="s">
         <v>29</v>
@@ -3223,7 +3223,7 @@
       <c r="V13" s="23"/>
     </row>
     <row r="14" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="140" t="s">
+      <c r="A14" s="150" t="s">
         <v>32</v>
       </c>
       <c r="B14" s="20" t="s">
@@ -3262,7 +3262,7 @@
       <c r="L14" s="7"/>
     </row>
     <row r="15" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="141"/>
+      <c r="A15" s="151"/>
       <c r="B15" s="20" t="s">
         <v>35</v>
       </c>
@@ -3311,7 +3311,7 @@
       </c>
     </row>
     <row r="16" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="142"/>
+      <c r="A16" s="152"/>
       <c r="B16" s="20" t="s">
         <v>153</v>
       </c>
@@ -3360,7 +3360,7 @@
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="140" t="s">
+      <c r="A17" s="150" t="s">
         <v>3</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -3405,7 +3405,7 @@
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="141"/>
+      <c r="A18" s="151"/>
       <c r="B18" s="8" t="s">
         <v>5</v>
       </c>
@@ -3469,7 +3469,7 @@
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="141"/>
+      <c r="A19" s="151"/>
       <c r="B19" s="8" t="s">
         <v>116</v>
       </c>
@@ -3530,7 +3530,7 @@
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="141"/>
+      <c r="A20" s="151"/>
       <c r="B20" s="8" t="s">
         <v>114</v>
       </c>
@@ -3565,7 +3565,7 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="142"/>
+      <c r="A21" s="152"/>
       <c r="B21" s="8" t="s">
         <v>115</v>
       </c>
@@ -3608,7 +3608,7 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="143" t="s">
+      <c r="A22" s="153" t="s">
         <v>12</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -3654,7 +3654,7 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="141"/>
+      <c r="A23" s="151"/>
       <c r="B23" s="6" t="s">
         <v>5</v>
       </c>
@@ -3707,7 +3707,7 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="141"/>
+      <c r="A24" s="151"/>
       <c r="B24" s="6" t="s">
         <v>116</v>
       </c>
@@ -3760,7 +3760,7 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="142"/>
+      <c r="A25" s="152"/>
       <c r="B25" s="6" t="s">
         <v>69</v>
       </c>
@@ -3808,10 +3808,10 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="144" t="s">
+      <c r="A26" s="137" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="145"/>
+      <c r="B26" s="138"/>
       <c r="C26" s="23"/>
       <c r="D26" s="44" t="s">
         <v>21</v>
@@ -3858,10 +3858,10 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="144" t="s">
+      <c r="A27" s="137" t="s">
         <v>15</v>
       </c>
-      <c r="B27" s="145"/>
+      <c r="B27" s="138"/>
       <c r="C27" s="23"/>
       <c r="D27" s="107">
         <v>0.42099999999999999</v>
@@ -3910,10 +3910,10 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="146" t="s">
+      <c r="A28" s="154" t="s">
         <v>13</v>
       </c>
-      <c r="B28" s="147"/>
+      <c r="B28" s="155"/>
       <c r="C28" s="101"/>
       <c r="D28" s="106">
         <v>79904</v>
@@ -3963,10 +3963,10 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="148" t="s">
+      <c r="A29" s="143" t="s">
         <v>14</v>
       </c>
-      <c r="B29" s="149"/>
+      <c r="B29" s="144"/>
       <c r="C29" s="102"/>
       <c r="D29" s="108">
         <f>+D28*(1-D27)</f>
@@ -4008,10 +4008,10 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="135" t="s">
+      <c r="A30" s="141" t="s">
         <v>23</v>
       </c>
-      <c r="B30" s="136"/>
+      <c r="B30" s="142"/>
       <c r="C30" s="30"/>
       <c r="D30" s="48">
         <v>4</v>
@@ -4050,37 +4050,38 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="144" t="s">
+      <c r="A31" s="137" t="s">
         <v>24</v>
       </c>
-      <c r="B31" s="145"/>
+      <c r="B31" s="138"/>
       <c r="C31" s="23"/>
       <c r="D31" s="108">
         <f>+D30*D29*0.75*0.41*0.07</f>
+        <v>3983.3662175999998</v>
       </c>
       <c r="E31" s="63">
         <f>+E29*E30*$P$24*$P$22*$P$23*$P$36</f>
-        <v>12856.223148122503</v>
+        <v>14998.927006142918</v>
       </c>
       <c r="F31" s="63">
         <f>+F29*F30*$P$24*$P$22*$P$23*$P$36</f>
-        <v>12852.250804698013</v>
+        <v>14994.292605481018</v>
       </c>
       <c r="G31" s="63">
         <f>+G29*G30*$P$24*$P$22*$P$23*$P$36</f>
-        <v>12821.647613504847</v>
+        <v>14958.588882422317</v>
       </c>
       <c r="H31" s="63">
         <f>+H29*H30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
-        <v>10229.262185475316</v>
+        <v>11934.139216387865</v>
       </c>
       <c r="I31" s="63">
         <f>+I29*I30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
-        <v>10197.600449769765</v>
+        <v>11897.200524731392</v>
       </c>
       <c r="J31" s="63">
         <f>+J29*J30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
-        <v>10162.299943972379</v>
+        <v>11856.016601301106</v>
       </c>
       <c r="K31" s="11"/>
       <c r="L31" s="7"/>
@@ -4091,10 +4092,10 @@
       <c r="Z31" s="35"/>
     </row>
     <row r="32" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="135" t="s">
+      <c r="A32" s="141" t="s">
         <v>30</v>
       </c>
-      <c r="B32" s="136"/>
+      <c r="B32" s="142"/>
       <c r="C32" s="30"/>
       <c r="D32" s="48">
         <v>0</v>
@@ -4138,10 +4139,10 @@
       <c r="Z32" s="35"/>
     </row>
     <row r="33" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="144" t="s">
+      <c r="A33" s="137" t="s">
         <v>31</v>
       </c>
-      <c r="B33" s="145"/>
+      <c r="B33" s="138"/>
       <c r="C33" s="23"/>
       <c r="D33" s="44">
         <v>0</v>
@@ -4184,37 +4185,38 @@
       </c>
     </row>
     <row r="34" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="148" t="s">
+      <c r="A34" s="143" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="149"/>
+      <c r="B34" s="144"/>
       <c r="C34" s="102"/>
       <c r="D34" s="108">
         <f>+D29*D30*0.75</f>
+        <v>138793.24799999999</v>
       </c>
       <c r="E34" s="46">
         <f>+E29*E30*$P$24+E26*E32</f>
-        <v>118124.88219158399</v>
+        <v>136887.64585684799</v>
       </c>
       <c r="F34" s="46">
         <f>+F29*F30*$P$24+F26*F32</f>
-        <v>118090.09803763201</v>
+        <v>136847.064343904</v>
       </c>
       <c r="G34" s="46">
         <f>+G29*G30*$P$24+G26*G32</f>
-        <v>117856.12991319555</v>
+        <v>136568.43299006144</v>
       </c>
       <c r="H34" s="46">
         <f>+H29*H30*$P$24*$Q$24+H26*H32</f>
-        <v>95190.043728529563</v>
+        <v>110118.9405471978</v>
       </c>
       <c r="I34" s="46">
         <f>+I29*I30*$P$24*$Q$24+I26*I32</f>
-        <v>94947.489997629338</v>
+        <v>109830.17871478669</v>
       </c>
       <c r="J34" s="46">
         <f>+J29*J30*$P$24*$Q$24+J26*J32</f>
-        <v>94673.420024053004</v>
+        <v>109504.59010778982</v>
       </c>
       <c r="K34" s="11"/>
       <c r="L34" s="7"/>
@@ -4230,38 +4232,38 @@
       </c>
     </row>
     <row r="35" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="148" t="s">
+      <c r="A35" s="143" t="s">
         <v>25</v>
       </c>
-      <c r="B35" s="149"/>
+      <c r="B35" s="144"/>
       <c r="C35" s="102"/>
       <c r="D35" s="109">
         <f>+D31*1.02</f>
-        <v>5417.3780559359993</v>
+        <v>4063.0335419519997</v>
       </c>
       <c r="E35" s="50">
         <f>+E31+E33+1.05*(E31+E33)</f>
-        <v>27804.042002326081</v>
+        <v>32196.584911267928</v>
       </c>
       <c r="F35" s="50">
         <f t="shared" ref="F35:J35" si="11">+F31+F33+1.05*(F31+F33)</f>
-        <v>27795.898698305871</v>
+        <v>32187.084389911033</v>
       </c>
       <c r="G35" s="50">
         <f t="shared" si="11"/>
-        <v>27742.043250497274</v>
+        <v>32122.772851778085</v>
       </c>
       <c r="H35" s="50">
         <f t="shared" si="11"/>
-        <v>22436.623028115493</v>
+        <v>25931.620941486217</v>
       </c>
       <c r="I35" s="50">
         <f t="shared" si="11"/>
-        <v>22380.77607404867</v>
+        <v>25864.956227720002</v>
       </c>
       <c r="J35" s="50">
         <f t="shared" si="11"/>
-        <v>22317.56023733487</v>
+        <v>25789.679384858762</v>
       </c>
       <c r="K35" s="11"/>
       <c r="L35" s="7"/>
@@ -4277,7 +4279,7 @@
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="150" t="s">
+      <c r="A36" s="145" t="s">
         <v>6</v>
       </c>
       <c r="B36" s="6" t="str">
@@ -4289,32 +4291,27 @@
         <v>0</v>
       </c>
       <c r="E36" s="111">
-        <f>ROUND(E35*0.004,0)</f>
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="F36" s="111">
-        <f>ROUND(F35*0.0045,0)</f>
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="G36" s="111">
-        <f>ROUND(G35*0.0055,0)</f>
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="H36" s="111">
-        <f>ROUND(H35*0.0065,0)</f>
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="I36" s="111">
-        <f>ROUND(I35*0.0075,0)</f>
-        <v>168</v>
+        <v>206</v>
       </c>
       <c r="J36" s="111">
         <f>ROUND(J35*0.009,0)</f>
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="K36" s="115">
         <f>SUM(E36:J36)</f>
-        <v>904</v>
+        <v>1093</v>
       </c>
       <c r="L36" s="7"/>
       <c r="N36" s="69" t="s">
@@ -4330,7 +4327,7 @@
       <c r="Q36" s="73"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="151"/>
+      <c r="A37" s="146"/>
       <c r="B37" s="6" t="str">
         <f>+C9</f>
         <v>-</v>
@@ -4367,7 +4364,7 @@
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="150" t="s">
+      <c r="A38" s="145" t="s">
         <v>9</v>
       </c>
       <c r="B38" s="6" t="str">
@@ -4409,7 +4406,7 @@
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="151"/>
+      <c r="A39" s="146"/>
       <c r="B39" s="6" t="str">
         <f>+C11</f>
         <v>-</v>
@@ -4449,10 +4446,10 @@
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="152" t="s">
+      <c r="A40" s="139" t="s">
         <v>53</v>
       </c>
-      <c r="B40" s="153"/>
+      <c r="B40" s="140"/>
       <c r="C40" s="97"/>
       <c r="D40" s="11">
         <f t="shared" ref="D40:J40" si="12">+SUM(D36:D39)</f>
@@ -4460,31 +4457,31 @@
       </c>
       <c r="E40" s="10">
         <f t="shared" si="12"/>
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="F40" s="10">
         <f t="shared" si="12"/>
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="G40" s="10">
         <f t="shared" si="12"/>
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="H40" s="10">
         <f t="shared" si="12"/>
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="I40" s="10">
         <f t="shared" si="12"/>
-        <v>168</v>
+        <v>206</v>
       </c>
       <c r="J40" s="10">
         <f t="shared" si="12"/>
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="K40" s="115">
         <f>SUM(E40:J40)</f>
-        <v>904</v>
+        <v>1093</v>
       </c>
       <c r="L40" s="7"/>
       <c r="O40" s="17"/>
@@ -4499,27 +4496,27 @@
       </c>
       <c r="E41" s="18">
         <f>+IFERROR(E40/E35,0)</f>
-        <v>3.9922253027352556E-3</v>
+        <v>4.4104056498956157E-3</v>
       </c>
       <c r="F41" s="18">
         <f t="shared" ref="F41:J41" si="14">+IFERROR(F40/F35,0)</f>
-        <v>4.4970663246667614E-3</v>
+        <v>4.8777328849708207E-3</v>
       </c>
       <c r="G41" s="18">
         <f t="shared" si="14"/>
-        <v>5.5150948550719125E-3</v>
+        <v>5.63463188047856E-3</v>
       </c>
       <c r="H41" s="18">
         <f t="shared" si="14"/>
-        <v>6.507218123558361E-3</v>
+        <v>6.7485175876541344E-3</v>
       </c>
       <c r="I41" s="18">
         <f t="shared" si="14"/>
-        <v>7.5064421110402043E-3</v>
+        <v>7.9644441763727248E-3</v>
       </c>
       <c r="J41" s="18">
         <f t="shared" si="14"/>
-        <v>9.0063608146444558E-3</v>
+        <v>8.9958466151466871E-3</v>
       </c>
       <c r="N41" s="69" t="s">
         <v>118</v>
@@ -4547,53 +4544,53 @@
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="144" t="s">
+      <c r="A44" s="137" t="s">
         <v>27</v>
       </c>
-      <c r="B44" s="145"/>
+      <c r="B44" s="138"/>
       <c r="C44" s="103"/>
       <c r="D44" s="16" t="s">
         <v>22</v>
       </c>
       <c r="E44" s="31">
         <f>+E75*E76</f>
-        <v>264374.646574752</v>
+        <v>320662.93757054396</v>
       </c>
       <c r="F44" s="31">
         <f t="shared" ref="F44:J44" si="15">+F75*F76</f>
-        <v>264270.29411289602</v>
+        <v>320541.19303171197</v>
       </c>
       <c r="G44" s="31">
         <f t="shared" si="15"/>
-        <v>263568.38973958662</v>
+        <v>319705.29897018429</v>
       </c>
       <c r="H44" s="31">
         <f t="shared" si="15"/>
-        <v>195570.13118558869</v>
+        <v>240356.82164159339</v>
       </c>
       <c r="I44" s="31">
         <f t="shared" si="15"/>
-        <v>194842.46999288801</v>
+        <v>239490.53614436006</v>
       </c>
       <c r="J44" s="31">
         <f t="shared" si="15"/>
-        <v>194020.260072159</v>
+        <v>238513.77032336945</v>
       </c>
       <c r="K44" s="11"/>
       <c r="L44" s="7"/>
     </row>
     <row r="45" spans="1:17" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="144" t="s">
+      <c r="A45" s="137" t="s">
         <v>132</v>
       </c>
-      <c r="B45" s="145"/>
+      <c r="B45" s="138"/>
       <c r="C45" s="104">
         <f>+SUM(C65:C72)</f>
         <v>0</v>
       </c>
       <c r="D45" s="80">
         <f>+SUM(D65:D72)</f>
-        <v>215000</v>
+        <v>165000</v>
       </c>
       <c r="E45" s="27">
         <f t="shared" ref="E45:J45" si="16">SUM(E65:E68)+SUM(E71:E72)</f>
@@ -4626,10 +4623,10 @@
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="144" t="s">
+      <c r="A46" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="B46" s="145"/>
+      <c r="B46" s="138"/>
       <c r="C46" s="103"/>
       <c r="D46" s="16" t="s">
         <v>22</v>
@@ -4662,118 +4659,118 @@
       <c r="L46" s="7"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="144" t="s">
+      <c r="A47" s="137" t="s">
         <v>18</v>
       </c>
-      <c r="B47" s="145"/>
+      <c r="B47" s="138"/>
       <c r="C47" s="103"/>
       <c r="D47" s="16" t="s">
         <v>22</v>
       </c>
       <c r="E47" s="28">
         <f t="shared" ref="E47:I47" si="18">+E51/E35</f>
-        <v>11.126966595319837</v>
+        <v>11.357196379003907</v>
       </c>
       <c r="F47" s="28">
         <f t="shared" si="18"/>
-        <v>11.126472198999117</v>
+        <v>11.356766229695847</v>
       </c>
       <c r="G47" s="28">
         <f t="shared" si="18"/>
-        <v>11.122770841115157</v>
+        <v>11.353481240645664</v>
       </c>
       <c r="H47" s="28">
         <f t="shared" si="18"/>
-        <v>10.72220765505257</v>
+        <v>11.004203026316439</v>
       </c>
       <c r="I47" s="28">
         <f t="shared" si="18"/>
-        <v>10.716450099824472</v>
+        <v>10.999072785573315</v>
       </c>
       <c r="J47" s="28">
         <f>+J51/J35</f>
-        <v>10.709963702587162</v>
+        <v>10.993303409961026</v>
       </c>
       <c r="K47" s="11"/>
       <c r="L47" s="7"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="144" t="s">
+      <c r="A48" s="137" t="s">
         <v>20</v>
       </c>
-      <c r="B48" s="145"/>
+      <c r="B48" s="138"/>
       <c r="C48" s="103"/>
       <c r="D48" s="16" t="s">
         <v>22</v>
       </c>
       <c r="E48" s="32">
         <f t="shared" ref="E48:J48" si="19">+SUM(E36:E39)/E35</f>
-        <v>3.9922253027352556E-3</v>
+        <v>4.4104056498956157E-3</v>
       </c>
       <c r="F48" s="32">
         <f t="shared" si="19"/>
-        <v>4.4970663246667614E-3</v>
+        <v>4.8777328849708207E-3</v>
       </c>
       <c r="G48" s="32">
         <f t="shared" si="19"/>
-        <v>5.5150948550719125E-3</v>
+        <v>5.63463188047856E-3</v>
       </c>
       <c r="H48" s="32">
         <f t="shared" si="19"/>
-        <v>6.507218123558361E-3</v>
+        <v>6.7485175876541344E-3</v>
       </c>
       <c r="I48" s="32">
         <f t="shared" si="19"/>
-        <v>7.5064421110402043E-3</v>
+        <v>7.9644441763727248E-3</v>
       </c>
       <c r="J48" s="32">
         <f t="shared" si="19"/>
-        <v>9.0063608146444558E-3</v>
+        <v>8.9958466151466871E-3</v>
       </c>
       <c r="K48" s="11"/>
       <c r="L48" s="7"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="152" t="s">
+      <c r="A49" s="139" t="s">
         <v>19</v>
       </c>
-      <c r="B49" s="153"/>
+      <c r="B49" s="140"/>
       <c r="C49" s="105"/>
       <c r="D49" s="16" t="s">
         <v>22</v>
       </c>
       <c r="E49" s="28">
         <f>+IFERROR(E51/SUM(E36:E39),0)</f>
-        <v>2787.1589781509188</v>
+        <v>2575.0911096517179</v>
       </c>
       <c r="F49" s="28">
         <f t="shared" ref="F49:J49" si="20">+IFERROR(F51/SUM(F36:F39),0)</f>
-        <v>2474.1623529031681</v>
+        <v>2328.287853705172</v>
       </c>
       <c r="G49" s="28">
         <f t="shared" si="20"/>
-        <v>2016.7868610430498</v>
+        <v>2014.9464031501896</v>
       </c>
       <c r="H49" s="28">
         <f t="shared" si="20"/>
-        <v>1647.7406245588265</v>
+        <v>1630.6104093805334</v>
       </c>
       <c r="I49" s="28">
         <f t="shared" si="20"/>
-        <v>1427.6337499576669</v>
+        <v>1381.0220201182528</v>
       </c>
       <c r="J49" s="28">
         <f t="shared" si="20"/>
-        <v>1189.1555227470596</v>
+        <v>1222.0421134627993</v>
       </c>
       <c r="K49" s="11"/>
       <c r="L49" s="7"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="152" t="s">
+      <c r="A50" s="139" t="s">
         <v>117</v>
       </c>
-      <c r="B50" s="153"/>
+      <c r="B50" s="140"/>
       <c r="C50" s="105"/>
       <c r="D50" s="64" t="s">
         <v>22</v>
@@ -4806,41 +4803,41 @@
       <c r="L50" s="7"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="154" t="s">
+      <c r="A51" s="135" t="s">
         <v>70</v>
       </c>
-      <c r="B51" s="155"/>
+      <c r="B51" s="136"/>
       <c r="C51" s="110">
         <f>+C45</f>
         <v>0</v>
       </c>
       <c r="D51" s="40">
         <f>+D45</f>
-        <v>215000</v>
+        <v>165000</v>
       </c>
       <c r="E51" s="40">
         <f>SUM(E45,E50)+E44</f>
-        <v>309374.646574752</v>
+        <v>365662.93757054396</v>
       </c>
       <c r="F51" s="40">
         <f t="shared" ref="F51:I51" si="22">SUM(F45,F50)+F44</f>
-        <v>309270.29411289602</v>
+        <v>365541.19303171197</v>
       </c>
       <c r="G51" s="40">
         <f t="shared" si="22"/>
-        <v>308568.38973958662</v>
+        <v>364705.29897018429</v>
       </c>
       <c r="H51" s="40">
         <f t="shared" si="22"/>
-        <v>240570.13118558869</v>
+        <v>285356.82164159336</v>
       </c>
       <c r="I51" s="40">
         <f t="shared" si="22"/>
-        <v>239842.46999288801</v>
+        <v>284490.53614436009</v>
       </c>
       <c r="J51" s="40">
         <f>SUM(J45,J50)+J44</f>
-        <v>239020.260072159</v>
+        <v>283513.77032336942</v>
       </c>
       <c r="K51" s="11"/>
       <c r="L51" s="7"/>
@@ -4863,38 +4860,38 @@
       </c>
     </row>
     <row r="54" spans="1:14" ht="18" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="144" t="s">
+      <c r="A54" s="137" t="s">
         <v>27</v>
       </c>
-      <c r="B54" s="145"/>
+      <c r="B54" s="138"/>
       <c r="C54" s="96"/>
       <c r="D54" s="28">
         <f>+D75*D76</f>
-        <v>465172.99199999997</v>
+        <v>326379.74399999995</v>
       </c>
       <c r="E54" s="28">
         <f t="shared" ref="E54:J54" si="23">+E75*E76</f>
-        <v>264374.646574752</v>
+        <v>320662.93757054396</v>
       </c>
       <c r="F54" s="28">
         <f t="shared" si="23"/>
-        <v>264270.29411289602</v>
+        <v>320541.19303171197</v>
       </c>
       <c r="G54" s="28">
         <f t="shared" si="23"/>
-        <v>263568.38973958662</v>
+        <v>319705.29897018429</v>
       </c>
       <c r="H54" s="28">
         <f t="shared" si="23"/>
-        <v>195570.13118558869</v>
+        <v>240356.82164159339</v>
       </c>
       <c r="I54" s="28">
         <f t="shared" si="23"/>
-        <v>194842.46999288801</v>
+        <v>239490.53614436006</v>
       </c>
       <c r="J54" s="28">
         <f t="shared" si="23"/>
-        <v>194020.260072159</v>
+        <v>238513.77032336945</v>
       </c>
       <c r="K54" s="11"/>
       <c r="L54" s="7"/>
@@ -4903,47 +4900,47 @@
       </c>
     </row>
     <row r="55" spans="1:14" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="144" t="s">
+      <c r="A55" s="137" t="s">
         <v>132</v>
       </c>
-      <c r="B55" s="145"/>
+      <c r="B55" s="138"/>
       <c r="C55" s="96"/>
       <c r="D55" s="27">
         <f>+SUM(D65:D72)</f>
-        <v>215000</v>
+        <v>165000</v>
       </c>
       <c r="E55" s="27">
         <f>SUM(E65:E72)+E54</f>
-        <v>609374.64657475194</v>
+        <v>565662.93757054396</v>
       </c>
       <c r="F55" s="27">
         <f t="shared" ref="F55:J55" si="24">SUM(F65:F72)+F54</f>
-        <v>609270.29411289608</v>
+        <v>565541.19303171197</v>
       </c>
       <c r="G55" s="27">
         <f t="shared" si="24"/>
-        <v>608568.38973958662</v>
+        <v>564705.29897018429</v>
       </c>
       <c r="H55" s="27">
         <f t="shared" si="24"/>
-        <v>540570.13118558866</v>
+        <v>485356.82164159336</v>
       </c>
       <c r="I55" s="27">
         <f t="shared" si="24"/>
-        <v>539842.46999288804</v>
+        <v>484490.53614436009</v>
       </c>
       <c r="J55" s="27">
         <f t="shared" si="24"/>
-        <v>539020.260072159</v>
+        <v>483513.77032336942</v>
       </c>
       <c r="K55" s="11"/>
       <c r="L55" s="7"/>
     </row>
     <row r="56" spans="1:14" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="144" t="s">
+      <c r="A56" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="B56" s="145"/>
+      <c r="B56" s="138"/>
       <c r="C56" s="96"/>
       <c r="D56" s="39" t="s">
         <v>22</v>
@@ -4976,116 +4973,116 @@
       <c r="L56" s="7"/>
     </row>
     <row r="57" spans="1:14" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="144" t="s">
+      <c r="A57" s="137" t="s">
         <v>18</v>
       </c>
-      <c r="B57" s="145"/>
+      <c r="B57" s="138"/>
       <c r="C57" s="96"/>
       <c r="D57" s="39" t="s">
         <v>22</v>
       </c>
       <c r="E57" s="28">
         <f>+E61/E35</f>
-        <v>21.916764710820527</v>
+        <v>17.569035322518861</v>
       </c>
       <c r="F57" s="28">
         <f t="shared" ref="F57:J57" si="26">+F61/F35</f>
-        <v>21.919431378199345</v>
+        <v>17.570438694626827</v>
       </c>
       <c r="G57" s="28">
         <f t="shared" si="26"/>
-        <v>21.93668232164832</v>
+        <v>17.579593815760095</v>
       </c>
       <c r="H57" s="28">
         <f t="shared" si="26"/>
-        <v>24.093203799350569</v>
+        <v>18.71679455506402</v>
       </c>
       <c r="I57" s="28">
         <f t="shared" si="26"/>
-        <v>24.120811012396267</v>
+        <v>18.731542859721589</v>
       </c>
       <c r="J57" s="28">
         <f t="shared" si="26"/>
-        <v>24.152293276683366</v>
+        <v>18.74834359543231</v>
       </c>
       <c r="K57" s="11"/>
       <c r="L57" s="7"/>
     </row>
     <row r="58" spans="1:14" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="144" t="s">
+      <c r="A58" s="137" t="s">
         <v>20</v>
       </c>
-      <c r="B58" s="145"/>
+      <c r="B58" s="138"/>
       <c r="C58" s="96"/>
       <c r="D58" s="39" t="s">
         <v>22</v>
       </c>
       <c r="E58" s="32">
         <f t="shared" ref="E58:J58" si="27">+SUM(E36:E39)/E35</f>
-        <v>3.9922253027352556E-3</v>
+        <v>4.4104056498956157E-3</v>
       </c>
       <c r="F58" s="32">
         <f t="shared" si="27"/>
-        <v>4.4970663246667614E-3</v>
+        <v>4.8777328849708207E-3</v>
       </c>
       <c r="G58" s="32">
         <f t="shared" si="27"/>
-        <v>5.5150948550719125E-3</v>
+        <v>5.63463188047856E-3</v>
       </c>
       <c r="H58" s="32">
         <f t="shared" si="27"/>
-        <v>6.507218123558361E-3</v>
+        <v>6.7485175876541344E-3</v>
       </c>
       <c r="I58" s="32">
         <f t="shared" si="27"/>
-        <v>7.5064421110402043E-3</v>
+        <v>7.9644441763727248E-3</v>
       </c>
       <c r="J58" s="32">
         <f t="shared" si="27"/>
-        <v>9.0063608146444558E-3</v>
+        <v>8.9958466151466871E-3</v>
       </c>
       <c r="K58" s="11"/>
       <c r="L58" s="7"/>
     </row>
     <row r="59" spans="1:14" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="152" t="s">
+      <c r="A59" s="139" t="s">
         <v>19</v>
       </c>
-      <c r="B59" s="153"/>
+      <c r="B59" s="140"/>
       <c r="C59" s="97"/>
       <c r="D59" s="28"/>
       <c r="E59" s="28">
         <f>+IFERROR(E55/E40,0)</f>
-        <v>5489.8616808536208</v>
+        <v>3983.5418138770701</v>
       </c>
       <c r="F59" s="28">
         <f t="shared" ref="F59:J59" si="28">+IFERROR(F55/F40,0)</f>
-        <v>4874.1623529031685</v>
+        <v>3602.1732040236429</v>
       </c>
       <c r="G59" s="28">
         <f t="shared" si="28"/>
-        <v>3977.57117476854</v>
+        <v>3119.9187788407971</v>
       </c>
       <c r="H59" s="28">
         <f t="shared" si="28"/>
-        <v>3702.5351451067718</v>
+        <v>2773.4675522376765</v>
       </c>
       <c r="I59" s="28">
         <f t="shared" si="28"/>
-        <v>3213.3480356719529</v>
+        <v>2351.8958065260199</v>
       </c>
       <c r="J59" s="28">
         <f t="shared" si="28"/>
-        <v>2681.6928361798955</v>
+        <v>2084.1110789800405</v>
       </c>
       <c r="K59" s="11"/>
       <c r="L59" s="7"/>
     </row>
     <row r="60" spans="1:14" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="152" t="s">
+      <c r="A60" s="139" t="s">
         <v>117</v>
       </c>
-      <c r="B60" s="153"/>
+      <c r="B60" s="140"/>
       <c r="C60" s="97"/>
       <c r="D60" s="28"/>
       <c r="E60" s="28"/>
@@ -5098,38 +5095,38 @@
       <c r="L60" s="7"/>
     </row>
     <row r="61" spans="1:14" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="154" t="s">
+      <c r="A61" s="135" t="s">
         <v>70</v>
       </c>
-      <c r="B61" s="155"/>
+      <c r="B61" s="136"/>
       <c r="C61" s="98"/>
       <c r="D61" s="40">
         <f>+D55</f>
-        <v>215000</v>
+        <v>165000</v>
       </c>
       <c r="E61" s="40">
         <f>+SUM(E65:E72)+E54</f>
-        <v>609374.64657475194</v>
+        <v>565662.93757054396</v>
       </c>
       <c r="F61" s="40">
         <f t="shared" ref="F61:J61" si="29">+SUM(F65:F72)+F54</f>
-        <v>609270.29411289608</v>
+        <v>565541.19303171197</v>
       </c>
       <c r="G61" s="40">
         <f t="shared" si="29"/>
-        <v>608568.38973958662</v>
+        <v>564705.29897018429</v>
       </c>
       <c r="H61" s="40">
         <f t="shared" si="29"/>
-        <v>540570.13118558866</v>
+        <v>485356.82164159336</v>
       </c>
       <c r="I61" s="40">
         <f t="shared" si="29"/>
-        <v>539842.46999288804</v>
+        <v>484490.53614436009</v>
       </c>
       <c r="J61" s="40">
         <f t="shared" si="29"/>
-        <v>539020.260072159</v>
+        <v>483513.77032336942</v>
       </c>
       <c r="K61" s="11"/>
       <c r="L61" s="7"/>
@@ -5429,31 +5426,31 @@
       </c>
       <c r="D73" s="114">
         <f>SUM(D65:D72)</f>
-        <v>215000</v>
+        <v>165000</v>
       </c>
       <c r="E73" s="114">
         <f t="shared" ref="E73:J73" si="31">SUM(E65:E72)+E54</f>
-        <v>609374.64657475194</v>
+        <v>565662.93757054396</v>
       </c>
       <c r="F73" s="114">
         <f t="shared" si="31"/>
-        <v>609270.29411289608</v>
+        <v>565541.19303171197</v>
       </c>
       <c r="G73" s="114">
         <f t="shared" si="31"/>
-        <v>608568.38973958662</v>
+        <v>564705.29897018429</v>
       </c>
       <c r="H73" s="114">
         <f t="shared" si="31"/>
-        <v>540570.13118558866</v>
+        <v>485356.82164159336</v>
       </c>
       <c r="I73" s="114">
         <f t="shared" si="31"/>
-        <v>539842.46999288804</v>
+        <v>484490.53614436009</v>
       </c>
       <c r="J73" s="114">
         <f t="shared" si="31"/>
-        <v>539020.260072159</v>
+        <v>483513.77032336942</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -5474,31 +5471,31 @@
       </c>
       <c r="D75" s="41">
         <f t="shared" ref="D75:J75" si="32">+IF(D34&lt;30001,0,D34-30000)</f>
-        <v>155057.66399999999</v>
+        <v>108793.24799999999</v>
       </c>
       <c r="E75" s="41">
         <f t="shared" si="32"/>
-        <v>88124.882191583994</v>
+        <v>106887.64585684799</v>
       </c>
       <c r="F75" s="41">
         <f t="shared" si="32"/>
-        <v>88090.098037632008</v>
+        <v>106847.064343904</v>
       </c>
       <c r="G75" s="41">
         <f t="shared" si="32"/>
-        <v>87856.129913195546</v>
+        <v>106568.43299006144</v>
       </c>
       <c r="H75" s="41">
         <f t="shared" si="32"/>
-        <v>65190.043728529563</v>
+        <v>80118.940547197795</v>
       </c>
       <c r="I75" s="41">
         <f t="shared" si="32"/>
-        <v>64947.489997629338</v>
+        <v>79830.178714786685</v>
       </c>
       <c r="J75" s="41">
         <f t="shared" si="32"/>
-        <v>64673.420024053004</v>
+        <v>79504.590107789816</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -5536,6 +5533,29 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A46:B46"/>
     <mergeCell ref="A61:B61"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A49:B49"/>
@@ -5548,29 +5568,6 @@
     <mergeCell ref="A58:B58"/>
     <mergeCell ref="A59:B59"/>
     <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5627,11 +5624,11 @@
       </c>
       <c r="D4" s="28">
         <f>+SIM①_月4投稿!G51</f>
-        <v>308568.38973958662</v>
+        <v>364705.29897018429</v>
       </c>
       <c r="E4" s="28">
         <f>+SIM①_月4投稿!J51</f>
-        <v>239020.260072159</v>
+        <v>283513.77032336942</v>
       </c>
       <c r="F4" s="28"/>
     </row>
@@ -5646,11 +5643,11 @@
       </c>
       <c r="D5" s="28">
         <f>+SIM①_月4投稿!G61</f>
-        <v>608568.38973958662</v>
+        <v>564705.29897018429</v>
       </c>
       <c r="E5" s="28">
         <f>+SIM①_月4投稿!J61</f>
-        <v>539020.260072159</v>
+        <v>483513.77032336942</v>
       </c>
       <c r="F5" s="27"/>
     </row>
@@ -5726,15 +5723,15 @@
       <c r="B10" s="7"/>
       <c r="C10" s="117">
         <f>+SIM①_月4投稿!D34</f>
-        <v>185057.66399999999</v>
+        <v>138793.24799999999</v>
       </c>
       <c r="D10" s="10">
         <f>+SIM①_月4投稿!G34</f>
-        <v>117856.12991319555</v>
+        <v>136568.43299006144</v>
       </c>
       <c r="E10" s="10">
         <f>+SIM①_月4投稿!J34</f>
-        <v>94673.420024053004</v>
+        <v>109504.59010778982</v>
       </c>
       <c r="F10" s="10"/>
     </row>
@@ -5745,15 +5742,15 @@
       <c r="B11" s="7"/>
       <c r="C11" s="117">
         <f>+SIM①_月4投稿!D35</f>
-        <v>5417.3780559359993</v>
+        <v>4063.0335419519997</v>
       </c>
       <c r="D11" s="10">
         <f>+SIM①_月4投稿!G35</f>
-        <v>27742.043250497274</v>
+        <v>32122.772851778085</v>
       </c>
       <c r="E11" s="10">
         <f>+SIM①_月4投稿!J35</f>
-        <v>22317.56023733487</v>
+        <v>25789.679384858762</v>
       </c>
       <c r="F11" s="10"/>
     </row>
@@ -5768,11 +5765,11 @@
       </c>
       <c r="D12" s="28">
         <f>+D4/D11</f>
-        <v>11.122770841115157</v>
+        <v>11.353481240645664</v>
       </c>
       <c r="E12" s="28">
         <f t="shared" ref="E12" si="0">+E4/E11</f>
-        <v>10.709963702587162</v>
+        <v>10.993303409961026</v>
       </c>
       <c r="F12" s="28"/>
     </row>
@@ -5787,11 +5784,11 @@
       </c>
       <c r="D13" s="28">
         <f>+D5/D11</f>
-        <v>21.93668232164832</v>
+        <v>17.579593815760095</v>
       </c>
       <c r="E13" s="28">
         <f t="shared" ref="E13" si="1">+E5/E11</f>
-        <v>24.152293276683366</v>
+        <v>18.74834359543231</v>
       </c>
       <c r="F13" s="28"/>
     </row>
@@ -5839,11 +5836,11 @@
       </c>
       <c r="D16" s="87">
         <f>+D17</f>
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="E16" s="87">
         <f>+E17</f>
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="F16" s="87"/>
       <c r="R16" s="5" t="s">
@@ -5867,11 +5864,11 @@
       </c>
       <c r="D17" s="87">
         <f>+SIM①_月4投稿!G36</f>
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="E17" s="87">
         <f>+SIM①_月4投稿!J36</f>
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="F17" s="10"/>
       <c r="R17" s="5">
@@ -6009,11 +6006,11 @@
       </c>
       <c r="D22" s="90">
         <f t="shared" ref="D22:E22" si="2">+IFERROR(D4/D16,"--")</f>
-        <v>2016.7868610430498</v>
+        <v>2014.9464031501896</v>
       </c>
       <c r="E22" s="90">
         <f t="shared" si="2"/>
-        <v>1189.1555227470596</v>
+        <v>1222.0421134627993</v>
       </c>
       <c r="F22" s="90"/>
       <c r="R22" s="34"/>
@@ -6033,11 +6030,11 @@
       </c>
       <c r="D23" s="90">
         <f t="shared" ref="D23" si="3">+IFERROR(D5/D16,"--")</f>
-        <v>3977.57117476854</v>
+        <v>3119.9187788407971</v>
       </c>
       <c r="E23" s="90">
         <f t="shared" ref="E23" si="4">+IFERROR(E5/E16,"--")</f>
-        <v>2681.6928361798955</v>
+        <v>2084.1110789800405</v>
       </c>
       <c r="F23" s="90"/>
       <c r="R23" s="34"/>
@@ -6066,15 +6063,15 @@
       <c r="B25" s="7"/>
       <c r="C25" s="10">
         <f>+SIM①_月4投稿!E68+C29*C30</f>
-        <v>480172.99199999997</v>
+        <v>341379.74399999995</v>
       </c>
       <c r="D25" s="10">
         <f>+SIM①_月4投稿!G68+D29*D30</f>
-        <v>278568.38973958662</v>
+        <v>334705.29897018429</v>
       </c>
       <c r="E25" s="10">
         <f>+SIM①_月4投稿!J68+E29*E30</f>
-        <v>209020.260072159</v>
+        <v>253513.77032336945</v>
       </c>
       <c r="F25" s="10"/>
       <c r="R25" s="34"/>
@@ -6110,15 +6107,15 @@
       </c>
       <c r="C29" s="5">
         <f>+IF(C10&lt;=30000,0,C10-30000)</f>
-        <v>155057.66399999999</v>
+        <v>108793.24799999999</v>
       </c>
       <c r="D29" s="91">
         <f>+IF(D10&lt;=30000,0,D10-30000)</f>
-        <v>87856.129913195546</v>
+        <v>106568.43299006144</v>
       </c>
       <c r="E29" s="91">
         <f>+IF(E10&lt;=30000,0,E10-30000)</f>
-        <v>64673.420024053004</v>
+        <v>79504.590107789816</v>
       </c>
       <c r="F29" s="91"/>
       <c r="R29" s="34"/>
@@ -6275,7 +6272,7 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="137" t="s">
+      <c r="A8" s="147" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="19" t="s">
@@ -6308,7 +6305,7 @@
       </c>
     </row>
     <row r="9" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="138"/>
+      <c r="A9" s="148"/>
       <c r="B9" s="19" t="s">
         <v>8</v>
       </c>
@@ -6338,7 +6335,7 @@
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="137" t="s">
+      <c r="A10" s="147" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="19" t="s">
@@ -6366,7 +6363,7 @@
       </c>
     </row>
     <row r="11" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="138"/>
+      <c r="A11" s="148"/>
       <c r="B11" s="19" t="s">
         <v>11</v>
       </c>
@@ -6400,10 +6397,10 @@
       <c r="V12" s="55"/>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="139" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="139"/>
+      <c r="A13" s="149" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="149"/>
       <c r="C13" s="95"/>
       <c r="D13" s="13" t="s">
         <v>29</v>
@@ -6446,7 +6443,7 @@
       <c r="V13" s="23"/>
     </row>
     <row r="14" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="140" t="s">
+      <c r="A14" s="150" t="s">
         <v>32</v>
       </c>
       <c r="B14" s="20" t="s">
@@ -6485,7 +6482,7 @@
       <c r="L14" s="7"/>
     </row>
     <row r="15" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="141"/>
+      <c r="A15" s="151"/>
       <c r="B15" s="20" t="s">
         <v>35</v>
       </c>
@@ -6534,7 +6531,7 @@
       </c>
     </row>
     <row r="16" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="142"/>
+      <c r="A16" s="152"/>
       <c r="B16" s="20" t="s">
         <v>153</v>
       </c>
@@ -6583,7 +6580,7 @@
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="140" t="s">
+      <c r="A17" s="150" t="s">
         <v>3</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -6628,7 +6625,7 @@
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="141"/>
+      <c r="A18" s="151"/>
       <c r="B18" s="8" t="s">
         <v>5</v>
       </c>
@@ -6692,7 +6689,7 @@
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="141"/>
+      <c r="A19" s="151"/>
       <c r="B19" s="8" t="s">
         <v>116</v>
       </c>
@@ -6753,7 +6750,7 @@
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="141"/>
+      <c r="A20" s="151"/>
       <c r="B20" s="8" t="s">
         <v>114</v>
       </c>
@@ -6788,7 +6785,7 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="142"/>
+      <c r="A21" s="152"/>
       <c r="B21" s="8" t="s">
         <v>115</v>
       </c>
@@ -6831,7 +6828,7 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="143" t="s">
+      <c r="A22" s="153" t="s">
         <v>12</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -6877,7 +6874,7 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="141"/>
+      <c r="A23" s="151"/>
       <c r="B23" s="6" t="s">
         <v>5</v>
       </c>
@@ -6930,7 +6927,7 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="141"/>
+      <c r="A24" s="151"/>
       <c r="B24" s="6" t="s">
         <v>116</v>
       </c>
@@ -6983,7 +6980,7 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="142"/>
+      <c r="A25" s="152"/>
       <c r="B25" s="6" t="s">
         <v>69</v>
       </c>
@@ -7031,10 +7028,10 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="144" t="s">
+      <c r="A26" s="137" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="145"/>
+      <c r="B26" s="138"/>
       <c r="C26" s="23"/>
       <c r="D26" s="44" t="s">
         <v>21</v>
@@ -7081,10 +7078,10 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="144" t="s">
+      <c r="A27" s="137" t="s">
         <v>15</v>
       </c>
-      <c r="B27" s="145"/>
+      <c r="B27" s="138"/>
       <c r="C27" s="23"/>
       <c r="D27" s="107">
         <v>0.42099999999999999</v>
@@ -7133,10 +7130,10 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="146" t="s">
+      <c r="A28" s="154" t="s">
         <v>13</v>
       </c>
-      <c r="B28" s="147"/>
+      <c r="B28" s="155"/>
       <c r="C28" s="101"/>
       <c r="D28" s="106">
         <v>79904</v>
@@ -7186,10 +7183,10 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="148" t="s">
+      <c r="A29" s="143" t="s">
         <v>14</v>
       </c>
-      <c r="B29" s="149"/>
+      <c r="B29" s="144"/>
       <c r="C29" s="102"/>
       <c r="D29" s="108">
         <f>+D28*(1-D27)</f>
@@ -7231,10 +7228,10 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="135" t="s">
+      <c r="A30" s="141" t="s">
         <v>23</v>
       </c>
-      <c r="B30" s="136"/>
+      <c r="B30" s="142"/>
       <c r="C30" s="30"/>
       <c r="D30" s="48">
         <v>4</v>
@@ -7273,37 +7270,38 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="144" t="s">
+      <c r="A31" s="137" t="s">
         <v>24</v>
       </c>
-      <c r="B31" s="145"/>
+      <c r="B31" s="138"/>
       <c r="C31" s="23"/>
       <c r="D31" s="108">
         <f>+D30*D29*0.75*0.41*0.07</f>
+        <v>3983.3662175999998</v>
       </c>
       <c r="E31" s="63">
         <f>+E29*E30*$P$24*$P$22*$P$23*$P$36</f>
-        <v>21427.038580204167</v>
+        <v>16070.278935153121</v>
       </c>
       <c r="F31" s="63">
         <f>+F29*F30*$P$24*$P$22*$P$23*$P$36</f>
-        <v>21420.418007830023</v>
+        <v>16065.313505872515</v>
       </c>
       <c r="G31" s="63">
         <f>+G29*G30*$P$24*$P$22*$P$23*$P$36</f>
-        <v>21369.41268917474</v>
+        <v>16027.059516881054</v>
       </c>
       <c r="H31" s="63">
         <f>+H29*H30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
-        <v>17048.770309125524</v>
+        <v>12786.57773184414</v>
       </c>
       <c r="I31" s="63">
         <f>+I29*I30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
-        <v>16996.000749616273</v>
+        <v>12747.000562212204</v>
       </c>
       <c r="J31" s="63">
         <f>+J29*J30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
-        <v>16937.166573287293</v>
+        <v>12702.874929965472</v>
       </c>
       <c r="K31" s="11"/>
       <c r="L31" s="7"/>
@@ -7314,10 +7312,10 @@
       <c r="Z31" s="35"/>
     </row>
     <row r="32" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="135" t="s">
+      <c r="A32" s="141" t="s">
         <v>30</v>
       </c>
-      <c r="B32" s="136"/>
+      <c r="B32" s="142"/>
       <c r="C32" s="30"/>
       <c r="D32" s="48">
         <v>0</v>
@@ -7361,10 +7359,10 @@
       <c r="Z32" s="35"/>
     </row>
     <row r="33" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="144" t="s">
+      <c r="A33" s="137" t="s">
         <v>31</v>
       </c>
-      <c r="B33" s="145"/>
+      <c r="B33" s="138"/>
       <c r="C33" s="23"/>
       <c r="D33" s="44">
         <v>0</v>
@@ -7407,37 +7405,38 @@
       </c>
     </row>
     <row r="34" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="148" t="s">
+      <c r="A34" s="143" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="149"/>
+      <c r="B34" s="144"/>
       <c r="C34" s="102"/>
       <c r="D34" s="108">
         <f>+D29*D30*0.75</f>
+        <v>138793.24799999999</v>
       </c>
       <c r="E34" s="46">
         <f>+E29*E30*$P$24+E26*E32</f>
-        <v>193175.93685263998</v>
+        <v>146269.02768947996</v>
       </c>
       <c r="F34" s="46">
         <f>+F29*F30*$P$24+F26*F32</f>
-        <v>193117.96326272</v>
+        <v>146225.54749703998</v>
       </c>
       <c r="G34" s="46">
         <f>+G29*G30*$P$24+G26*G32</f>
-        <v>192705.34222065922</v>
+        <v>145924.58452849439</v>
       </c>
       <c r="H34" s="46">
         <f>+H29*H30*$P$24*$Q$24+H26*H32</f>
-        <v>154905.63100320258</v>
+        <v>117583.38895653191</v>
       </c>
       <c r="I34" s="46">
         <f>+I29*I30*$P$24*$Q$24+I26*I32</f>
-        <v>154478.24486625876</v>
+        <v>117271.52307336536</v>
       </c>
       <c r="J34" s="46">
         <f>+J29*J30*$P$24*$Q$24+J26*J32</f>
-        <v>153998.10035900029</v>
+        <v>116920.17514965823</v>
       </c>
       <c r="K34" s="11"/>
       <c r="L34" s="7"/>
@@ -7453,38 +7452,38 @@
       </c>
     </row>
     <row r="35" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="148" t="s">
+      <c r="A35" s="143" t="s">
         <v>25</v>
       </c>
-      <c r="B35" s="149"/>
+      <c r="B35" s="144"/>
       <c r="C35" s="102"/>
       <c r="D35" s="109">
         <f>+D31*1.02</f>
-        <v>5417.3780559359993</v>
+        <v>4063.0335419519997</v>
       </c>
       <c r="E35" s="50">
         <f>+E31+E33+1.05*(E31+E33)</f>
-        <v>45374.213638093497</v>
+        <v>34392.856365738844</v>
       </c>
       <c r="F35" s="50">
         <f t="shared" ref="F35:J35" si="11">+F31+F33+1.05*(F31+F33)</f>
-        <v>45360.641464726497</v>
+        <v>34382.6772357136</v>
       </c>
       <c r="G35" s="50">
         <f t="shared" si="11"/>
-        <v>45264.961655620551</v>
+        <v>34313.137652418496</v>
       </c>
       <c r="H35" s="50">
         <f t="shared" si="11"/>
-        <v>36416.614681598425</v>
+        <v>27679.119898171582</v>
       </c>
       <c r="I35" s="50">
         <f t="shared" si="11"/>
-        <v>36317.496688734012</v>
+        <v>27607.046304555668</v>
       </c>
       <c r="J35" s="50">
         <f t="shared" si="11"/>
-        <v>36206.036827430449</v>
+        <v>27525.73895862071</v>
       </c>
       <c r="K35" s="11"/>
       <c r="L35" s="7"/>
@@ -7500,7 +7499,7 @@
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="150" t="s">
+      <c r="A36" s="145" t="s">
         <v>6</v>
       </c>
       <c r="B36" s="6" t="str">
@@ -7512,32 +7511,26 @@
         <v>0</v>
       </c>
       <c r="E36" s="111">
-        <f>ROUND(E35*0.004,0)</f>
-        <v>181</v>
+        <v>146</v>
       </c>
       <c r="F36" s="111">
-        <f>ROUND(F35*0.0045,0)</f>
-        <v>204</v>
+        <v>168</v>
       </c>
       <c r="G36" s="111">
-        <f>ROUND(G35*0.0055,0)</f>
-        <v>249</v>
+        <v>192</v>
       </c>
       <c r="H36" s="111">
-        <f>ROUND(H35*0.0065,0)</f>
-        <v>237</v>
+        <v>209</v>
       </c>
       <c r="I36" s="111">
-        <f>ROUND(I35*0.0075,0)</f>
-        <v>272</v>
+        <v>225</v>
       </c>
       <c r="J36" s="111">
-        <f>ROUND(J35*0.009,0)</f>
-        <v>326</v>
+        <v>253</v>
       </c>
       <c r="K36" s="115">
         <f>SUM(E36:J36)</f>
-        <v>1469</v>
+        <v>1193</v>
       </c>
       <c r="L36" s="7"/>
       <c r="N36" s="69" t="s">
@@ -7553,7 +7546,7 @@
       <c r="Q36" s="73"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="151"/>
+      <c r="A37" s="146"/>
       <c r="B37" s="6" t="str">
         <f>+C9</f>
         <v>-</v>
@@ -7590,7 +7583,7 @@
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="150" t="s">
+      <c r="A38" s="145" t="s">
         <v>9</v>
       </c>
       <c r="B38" s="6" t="str">
@@ -7632,7 +7625,7 @@
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="151"/>
+      <c r="A39" s="146"/>
       <c r="B39" s="6" t="str">
         <f>+C11</f>
         <v>-</v>
@@ -7672,10 +7665,10 @@
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="152" t="s">
+      <c r="A40" s="139" t="s">
         <v>53</v>
       </c>
-      <c r="B40" s="153"/>
+      <c r="B40" s="140"/>
       <c r="C40" s="97"/>
       <c r="D40" s="11">
         <f t="shared" ref="D40:J40" si="12">+SUM(D36:D39)</f>
@@ -7683,31 +7676,31 @@
       </c>
       <c r="E40" s="10">
         <f t="shared" si="12"/>
-        <v>181</v>
+        <v>146</v>
       </c>
       <c r="F40" s="10">
         <f t="shared" si="12"/>
-        <v>204</v>
+        <v>168</v>
       </c>
       <c r="G40" s="10">
         <f t="shared" si="12"/>
-        <v>249</v>
+        <v>192</v>
       </c>
       <c r="H40" s="10">
         <f t="shared" si="12"/>
-        <v>237</v>
+        <v>209</v>
       </c>
       <c r="I40" s="10">
         <f t="shared" si="12"/>
-        <v>272</v>
+        <v>225</v>
       </c>
       <c r="J40" s="10">
         <f t="shared" si="12"/>
-        <v>326</v>
+        <v>253</v>
       </c>
       <c r="K40" s="115">
         <f>SUM(E40:J40)</f>
-        <v>1469</v>
+        <v>1193</v>
       </c>
       <c r="L40" s="7"/>
       <c r="O40" s="17"/>
@@ -7722,27 +7715,27 @@
       </c>
       <c r="E41" s="18">
         <f>+IFERROR(E40/E35,0)</f>
-        <v>3.9890498476439305E-3</v>
+        <v>4.2450675933226913E-3</v>
       </c>
       <c r="F41" s="18">
         <f t="shared" ref="F41:J41" si="14">+IFERROR(F40/F35,0)</f>
-        <v>4.4972908982919739E-3</v>
+        <v>4.8861814584204881E-3</v>
       </c>
       <c r="G41" s="18">
         <f t="shared" si="14"/>
-        <v>5.5009435751743685E-3</v>
+        <v>5.5955244298816625E-3</v>
       </c>
       <c r="H41" s="18">
         <f t="shared" si="14"/>
-        <v>6.5080184435638323E-3</v>
+        <v>7.5508181173710677E-3</v>
       </c>
       <c r="I41" s="18">
         <f t="shared" si="14"/>
-        <v>7.4895029889099334E-3</v>
+        <v>8.1500931870017133E-3</v>
       </c>
       <c r="J41" s="18">
         <f t="shared" si="14"/>
-        <v>9.004023322238229E-3</v>
+        <v>9.1913972002834691E-3</v>
       </c>
       <c r="N41" s="69" t="s">
         <v>118</v>
@@ -7770,53 +7763,53 @@
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="144" t="s">
+      <c r="A44" s="137" t="s">
         <v>27</v>
       </c>
-      <c r="B44" s="145"/>
+      <c r="B44" s="138"/>
       <c r="C44" s="103"/>
       <c r="D44" s="16" t="s">
         <v>22</v>
       </c>
       <c r="E44" s="31">
         <f>+E75*E76</f>
-        <v>489527.8105579199</v>
+        <v>348807.08306843985</v>
       </c>
       <c r="F44" s="31">
         <f t="shared" ref="F44:J44" si="15">+F75*F76</f>
-        <v>489353.88978815998</v>
+        <v>348676.64249111991</v>
       </c>
       <c r="G44" s="31">
         <f t="shared" si="15"/>
-        <v>488116.02666197764</v>
+        <v>347773.75358548318</v>
       </c>
       <c r="H44" s="31">
         <f t="shared" si="15"/>
-        <v>374716.89300960774</v>
+        <v>262750.16686959576</v>
       </c>
       <c r="I44" s="31">
         <f t="shared" si="15"/>
-        <v>373434.73459877627</v>
+        <v>261814.56922009608</v>
       </c>
       <c r="J44" s="31">
         <f t="shared" si="15"/>
-        <v>371994.30107700091</v>
+        <v>260760.52544897469</v>
       </c>
       <c r="K44" s="11"/>
       <c r="L44" s="7"/>
     </row>
     <row r="45" spans="1:17" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="144" t="s">
+      <c r="A45" s="137" t="s">
         <v>132</v>
       </c>
-      <c r="B45" s="145"/>
+      <c r="B45" s="138"/>
       <c r="C45" s="104">
         <f>+SUM(C65:C72)</f>
         <v>0</v>
       </c>
       <c r="D45" s="80">
         <f>+SUM(D65:D72)</f>
-        <v>265000</v>
+        <v>215000</v>
       </c>
       <c r="E45" s="27">
         <f t="shared" ref="E45:J45" si="16">SUM(E65:E68)+SUM(E71:E72)</f>
@@ -7849,10 +7842,10 @@
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="144" t="s">
+      <c r="A46" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="B46" s="145"/>
+      <c r="B46" s="138"/>
       <c r="C46" s="103"/>
       <c r="D46" s="16" t="s">
         <v>22</v>
@@ -7885,118 +7878,118 @@
       <c r="L46" s="7"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="144" t="s">
+      <c r="A47" s="137" t="s">
         <v>18</v>
       </c>
-      <c r="B47" s="145"/>
+      <c r="B47" s="138"/>
       <c r="C47" s="103"/>
       <c r="D47" s="16" t="s">
         <v>22</v>
       </c>
       <c r="E47" s="28">
         <f t="shared" ref="E47:I47" si="18">+E51/E35</f>
-        <v>11.780431388218309</v>
+        <v>11.45025812571761</v>
       </c>
       <c r="F47" s="28">
         <f t="shared" si="18"/>
-        <v>11.780121985349043</v>
+        <v>11.449854233055603</v>
       </c>
       <c r="G47" s="28">
         <f t="shared" si="18"/>
-        <v>11.777675428468648</v>
+        <v>11.446745487520266</v>
       </c>
       <c r="H47" s="28">
         <f t="shared" si="18"/>
-        <v>11.525423125661751</v>
+        <v>11.118495385755564</v>
       </c>
       <c r="I47" s="28">
         <f t="shared" si="18"/>
-        <v>11.521574247945845</v>
+        <v>11.113632578993649</v>
       </c>
       <c r="J47" s="28">
         <f>+J51/J35</f>
-        <v>11.517258932937873</v>
+        <v>11.108167737426514</v>
       </c>
       <c r="K47" s="11"/>
       <c r="L47" s="7"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="144" t="s">
+      <c r="A48" s="137" t="s">
         <v>20</v>
       </c>
-      <c r="B48" s="145"/>
+      <c r="B48" s="138"/>
       <c r="C48" s="103"/>
       <c r="D48" s="16" t="s">
         <v>22</v>
       </c>
       <c r="E48" s="32">
         <f t="shared" ref="E48:J48" si="19">+SUM(E36:E39)/E35</f>
-        <v>3.9890498476439305E-3</v>
+        <v>4.2450675933226913E-3</v>
       </c>
       <c r="F48" s="32">
         <f t="shared" si="19"/>
-        <v>4.4972908982919739E-3</v>
+        <v>4.8861814584204881E-3</v>
       </c>
       <c r="G48" s="32">
         <f t="shared" si="19"/>
-        <v>5.5009435751743685E-3</v>
+        <v>5.5955244298816625E-3</v>
       </c>
       <c r="H48" s="32">
         <f t="shared" si="19"/>
-        <v>6.5080184435638323E-3</v>
+        <v>7.5508181173710677E-3</v>
       </c>
       <c r="I48" s="32">
         <f t="shared" si="19"/>
-        <v>7.4895029889099334E-3</v>
+        <v>8.1500931870017133E-3</v>
       </c>
       <c r="J48" s="32">
         <f t="shared" si="19"/>
-        <v>9.004023322238229E-3</v>
+        <v>9.1913972002834691E-3</v>
       </c>
       <c r="K48" s="11"/>
       <c r="L48" s="7"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="152" t="s">
+      <c r="A49" s="139" t="s">
         <v>19</v>
       </c>
-      <c r="B49" s="153"/>
+      <c r="B49" s="140"/>
       <c r="C49" s="105"/>
       <c r="D49" s="16" t="s">
         <v>22</v>
       </c>
       <c r="E49" s="28">
         <f>+IFERROR(E51/SUM(E36:E39),0)</f>
-        <v>2953.1923235244194</v>
+        <v>2697.3087881399988</v>
       </c>
       <c r="F49" s="28">
         <f t="shared" ref="F49:J49" si="20">+IFERROR(F51/SUM(F36:F39),0)</f>
-        <v>2619.3818126870588</v>
+        <v>2343.3133481614282</v>
       </c>
       <c r="G49" s="28">
         <f t="shared" si="20"/>
-        <v>2141.0282195260147</v>
+        <v>2045.6966332577249</v>
       </c>
       <c r="H49" s="28">
         <f t="shared" si="20"/>
-        <v>1770.9573544709187</v>
+        <v>1472.4888366966304</v>
       </c>
       <c r="I49" s="28">
         <f t="shared" si="20"/>
-        <v>1538.3629948484422</v>
+        <v>1363.6203076448717</v>
       </c>
       <c r="J49" s="28">
         <f t="shared" si="20"/>
-        <v>1279.1236229355857</v>
+        <v>1208.5396262805323</v>
       </c>
       <c r="K49" s="11"/>
       <c r="L49" s="7"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="152" t="s">
+      <c r="A50" s="139" t="s">
         <v>117</v>
       </c>
-      <c r="B50" s="153"/>
+      <c r="B50" s="140"/>
       <c r="C50" s="105"/>
       <c r="D50" s="64" t="s">
         <v>22</v>
@@ -8029,41 +8022,41 @@
       <c r="L50" s="7"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="154" t="s">
+      <c r="A51" s="135" t="s">
         <v>70</v>
       </c>
-      <c r="B51" s="155"/>
+      <c r="B51" s="136"/>
       <c r="C51" s="110">
         <f>+C45</f>
         <v>0</v>
       </c>
       <c r="D51" s="40">
         <f>+D45</f>
-        <v>265000</v>
+        <v>215000</v>
       </c>
       <c r="E51" s="40">
         <f>SUM(E45,E50)+E44</f>
-        <v>534527.8105579199</v>
+        <v>393807.08306843985</v>
       </c>
       <c r="F51" s="40">
         <f t="shared" ref="F51:I51" si="22">SUM(F45,F50)+F44</f>
-        <v>534353.88978815998</v>
+        <v>393676.64249111991</v>
       </c>
       <c r="G51" s="40">
         <f t="shared" si="22"/>
-        <v>533116.02666197764</v>
+        <v>392773.75358548318</v>
       </c>
       <c r="H51" s="40">
         <f t="shared" si="22"/>
-        <v>419716.89300960774</v>
+        <v>307750.16686959576</v>
       </c>
       <c r="I51" s="40">
         <f t="shared" si="22"/>
-        <v>418434.73459877627</v>
+        <v>306814.56922009611</v>
       </c>
       <c r="J51" s="40">
         <f>SUM(J45,J50)+J44</f>
-        <v>416994.30107700091</v>
+        <v>305760.52544897469</v>
       </c>
       <c r="K51" s="11"/>
       <c r="L51" s="7"/>
@@ -8086,38 +8079,38 @@
       </c>
     </row>
     <row r="54" spans="1:14" ht="18" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="144" t="s">
+      <c r="A54" s="137" t="s">
         <v>27</v>
       </c>
-      <c r="B54" s="145"/>
+      <c r="B54" s="138"/>
       <c r="C54" s="96"/>
       <c r="D54" s="28">
         <f>+D75*D76</f>
-        <v>465172.99199999997</v>
+        <v>326379.74399999995</v>
       </c>
       <c r="E54" s="28">
         <f t="shared" ref="E54:J54" si="23">+E75*E76</f>
-        <v>489527.8105579199</v>
+        <v>348807.08306843985</v>
       </c>
       <c r="F54" s="28">
         <f t="shared" si="23"/>
-        <v>489353.88978815998</v>
+        <v>348676.64249111991</v>
       </c>
       <c r="G54" s="28">
         <f t="shared" si="23"/>
-        <v>488116.02666197764</v>
+        <v>347773.75358548318</v>
       </c>
       <c r="H54" s="28">
         <f t="shared" si="23"/>
-        <v>374716.89300960774</v>
+        <v>262750.16686959576</v>
       </c>
       <c r="I54" s="28">
         <f t="shared" si="23"/>
-        <v>373434.73459877627</v>
+        <v>261814.56922009608</v>
       </c>
       <c r="J54" s="28">
         <f t="shared" si="23"/>
-        <v>371994.30107700091</v>
+        <v>260760.52544897469</v>
       </c>
       <c r="K54" s="11"/>
       <c r="L54" s="7"/>
@@ -8126,47 +8119,47 @@
       </c>
     </row>
     <row r="55" spans="1:14" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="144" t="s">
+      <c r="A55" s="137" t="s">
         <v>132</v>
       </c>
-      <c r="B55" s="145"/>
+      <c r="B55" s="138"/>
       <c r="C55" s="96"/>
       <c r="D55" s="27">
         <f>+SUM(D65:D72)</f>
-        <v>265000</v>
+        <v>215000</v>
       </c>
       <c r="E55" s="27">
         <f>SUM(E65:E72)+E54</f>
-        <v>884527.8105579199</v>
+        <v>693807.08306843985</v>
       </c>
       <c r="F55" s="27">
         <f t="shared" ref="F55:J55" si="24">SUM(F65:F72)+F54</f>
-        <v>884353.88978815998</v>
+        <v>693676.64249111991</v>
       </c>
       <c r="G55" s="27">
         <f t="shared" si="24"/>
-        <v>883116.02666197764</v>
+        <v>692773.75358548318</v>
       </c>
       <c r="H55" s="27">
         <f t="shared" si="24"/>
-        <v>769716.89300960768</v>
+        <v>607750.16686959576</v>
       </c>
       <c r="I55" s="27">
         <f t="shared" si="24"/>
-        <v>768434.73459877633</v>
+        <v>606814.56922009611</v>
       </c>
       <c r="J55" s="27">
         <f t="shared" si="24"/>
-        <v>766994.30107700091</v>
+        <v>605760.52544897469</v>
       </c>
       <c r="K55" s="11"/>
       <c r="L55" s="7"/>
     </row>
     <row r="56" spans="1:14" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="144" t="s">
+      <c r="A56" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="B56" s="145"/>
+      <c r="B56" s="138"/>
       <c r="C56" s="96"/>
       <c r="D56" s="39" t="s">
         <v>22</v>
@@ -8199,116 +8192,116 @@
       <c r="L56" s="7"/>
     </row>
     <row r="57" spans="1:14" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="144" t="s">
+      <c r="A57" s="137" t="s">
         <v>18</v>
       </c>
-      <c r="B57" s="145"/>
+      <c r="B57" s="138"/>
       <c r="C57" s="96"/>
       <c r="D57" s="39" t="s">
         <v>22</v>
       </c>
       <c r="E57" s="28">
         <f>+E61/E35</f>
-        <v>19.494063690292208</v>
+        <v>20.172999755832731</v>
       </c>
       <c r="F57" s="28">
         <f t="shared" ref="F57:J57" si="26">+F61/F35</f>
-        <v>19.496062252026448</v>
+        <v>20.175178265949334</v>
       </c>
       <c r="G57" s="28">
         <f t="shared" si="26"/>
-        <v>19.509925433733823</v>
+        <v>20.189752409210364</v>
       </c>
       <c r="H57" s="28">
         <f t="shared" si="26"/>
-        <v>21.136420827127324</v>
+        <v>21.956990291072884</v>
       </c>
       <c r="I57" s="28">
         <f t="shared" si="26"/>
-        <v>21.15880235867554</v>
+        <v>21.980423494995936</v>
       </c>
       <c r="J57" s="28">
         <f t="shared" si="26"/>
-        <v>21.184155137794868</v>
+        <v>22.007057698236952</v>
       </c>
       <c r="K57" s="11"/>
       <c r="L57" s="7"/>
     </row>
     <row r="58" spans="1:14" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="144" t="s">
+      <c r="A58" s="137" t="s">
         <v>20</v>
       </c>
-      <c r="B58" s="145"/>
+      <c r="B58" s="138"/>
       <c r="C58" s="96"/>
       <c r="D58" s="39" t="s">
         <v>22</v>
       </c>
       <c r="E58" s="32">
         <f t="shared" ref="E58:J58" si="27">+SUM(E36:E39)/E35</f>
-        <v>3.9890498476439305E-3</v>
+        <v>4.2450675933226913E-3</v>
       </c>
       <c r="F58" s="32">
         <f t="shared" si="27"/>
-        <v>4.4972908982919739E-3</v>
+        <v>4.8861814584204881E-3</v>
       </c>
       <c r="G58" s="32">
         <f t="shared" si="27"/>
-        <v>5.5009435751743685E-3</v>
+        <v>5.5955244298816625E-3</v>
       </c>
       <c r="H58" s="32">
         <f t="shared" si="27"/>
-        <v>6.5080184435638323E-3</v>
+        <v>7.5508181173710677E-3</v>
       </c>
       <c r="I58" s="32">
         <f t="shared" si="27"/>
-        <v>7.4895029889099334E-3</v>
+        <v>8.1500931870017133E-3</v>
       </c>
       <c r="J58" s="32">
         <f t="shared" si="27"/>
-        <v>9.004023322238229E-3</v>
+        <v>9.1913972002834691E-3</v>
       </c>
       <c r="K58" s="11"/>
       <c r="L58" s="7"/>
     </row>
     <row r="59" spans="1:14" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="152" t="s">
+      <c r="A59" s="139" t="s">
         <v>19</v>
       </c>
-      <c r="B59" s="153"/>
+      <c r="B59" s="140"/>
       <c r="C59" s="97"/>
       <c r="D59" s="28"/>
       <c r="E59" s="28">
         <f>+IFERROR(E55/E40,0)</f>
-        <v>4886.8939809829826</v>
+        <v>4752.1033086879443</v>
       </c>
       <c r="F59" s="28">
         <f t="shared" ref="F59:J59" si="28">+IFERROR(F55/F40,0)</f>
-        <v>4335.0680871968625</v>
+        <v>4129.0276338757139</v>
       </c>
       <c r="G59" s="28">
         <f t="shared" si="28"/>
-        <v>3546.6507094858539</v>
+        <v>3608.1966332577249</v>
       </c>
       <c r="H59" s="28">
         <f t="shared" si="28"/>
-        <v>3247.750603416066</v>
+        <v>2907.8955352612238</v>
       </c>
       <c r="I59" s="28">
         <f t="shared" si="28"/>
-        <v>2825.1277007307954</v>
+        <v>2696.9536409782049</v>
       </c>
       <c r="J59" s="28">
         <f t="shared" si="28"/>
-        <v>2352.7432548374263</v>
+        <v>2394.3103772686745</v>
       </c>
       <c r="K59" s="11"/>
       <c r="L59" s="7"/>
     </row>
     <row r="60" spans="1:14" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="152" t="s">
+      <c r="A60" s="139" t="s">
         <v>117</v>
       </c>
-      <c r="B60" s="153"/>
+      <c r="B60" s="140"/>
       <c r="C60" s="97"/>
       <c r="D60" s="28"/>
       <c r="E60" s="28"/>
@@ -8321,38 +8314,38 @@
       <c r="L60" s="7"/>
     </row>
     <row r="61" spans="1:14" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="154" t="s">
+      <c r="A61" s="135" t="s">
         <v>70</v>
       </c>
-      <c r="B61" s="155"/>
+      <c r="B61" s="136"/>
       <c r="C61" s="98"/>
       <c r="D61" s="40">
         <f>+D55</f>
-        <v>265000</v>
+        <v>215000</v>
       </c>
       <c r="E61" s="40">
         <f>+SUM(E65:E72)+E54</f>
-        <v>884527.8105579199</v>
+        <v>693807.08306843985</v>
       </c>
       <c r="F61" s="40">
         <f t="shared" ref="F61:J61" si="29">+SUM(F65:F72)+F54</f>
-        <v>884353.88978815998</v>
+        <v>693676.64249111991</v>
       </c>
       <c r="G61" s="40">
         <f t="shared" si="29"/>
-        <v>883116.02666197764</v>
+        <v>692773.75358548318</v>
       </c>
       <c r="H61" s="40">
         <f t="shared" si="29"/>
-        <v>769716.89300960768</v>
+        <v>607750.16686959576</v>
       </c>
       <c r="I61" s="40">
         <f t="shared" si="29"/>
-        <v>768434.73459877633</v>
+        <v>606814.56922009611</v>
       </c>
       <c r="J61" s="40">
         <f t="shared" si="29"/>
-        <v>766994.30107700091</v>
+        <v>605760.52544897469</v>
       </c>
       <c r="K61" s="11"/>
       <c r="L61" s="7"/>
@@ -8652,31 +8645,31 @@
       </c>
       <c r="D73" s="114">
         <f>SUM(D65:D72)</f>
-        <v>265000</v>
+        <v>215000</v>
       </c>
       <c r="E73" s="114">
         <f t="shared" ref="E73:J73" si="31">SUM(E65:E72)+E54</f>
-        <v>884527.8105579199</v>
+        <v>693807.08306843985</v>
       </c>
       <c r="F73" s="114">
         <f t="shared" si="31"/>
-        <v>884353.88978815998</v>
+        <v>693676.64249111991</v>
       </c>
       <c r="G73" s="114">
         <f t="shared" si="31"/>
-        <v>883116.02666197764</v>
+        <v>692773.75358548318</v>
       </c>
       <c r="H73" s="114">
         <f t="shared" si="31"/>
-        <v>769716.89300960768</v>
+        <v>607750.16686959576</v>
       </c>
       <c r="I73" s="114">
         <f t="shared" si="31"/>
-        <v>768434.73459877633</v>
+        <v>606814.56922009611</v>
       </c>
       <c r="J73" s="114">
         <f t="shared" si="31"/>
-        <v>766994.30107700091</v>
+        <v>605760.52544897469</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -8697,31 +8690,31 @@
       </c>
       <c r="D75" s="41">
         <f t="shared" ref="D75:J75" si="32">+IF(D34&lt;30001,0,D34-30000)</f>
-        <v>155057.66399999999</v>
+        <v>108793.24799999999</v>
       </c>
       <c r="E75" s="41">
         <f t="shared" si="32"/>
-        <v>163175.93685263998</v>
+        <v>116269.02768947996</v>
       </c>
       <c r="F75" s="41">
         <f t="shared" si="32"/>
-        <v>163117.96326272</v>
+        <v>116225.54749703998</v>
       </c>
       <c r="G75" s="41">
         <f t="shared" si="32"/>
-        <v>162705.34222065922</v>
+        <v>115924.58452849439</v>
       </c>
       <c r="H75" s="41">
         <f t="shared" si="32"/>
-        <v>124905.63100320258</v>
+        <v>87583.388956531911</v>
       </c>
       <c r="I75" s="41">
         <f t="shared" si="32"/>
-        <v>124478.24486625876</v>
+        <v>87271.523073365359</v>
       </c>
       <c r="J75" s="41">
         <f t="shared" si="32"/>
-        <v>123998.10035900029</v>
+        <v>86920.175149658229</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -8759,6 +8752,29 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A46:B46"/>
     <mergeCell ref="A61:B61"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A49:B49"/>
@@ -8771,29 +8787,6 @@
     <mergeCell ref="A58:B58"/>
     <mergeCell ref="A59:B59"/>
     <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8850,11 +8843,11 @@
       </c>
       <c r="D4" s="28">
         <f>+SIM②_月5投稿!G51</f>
-        <v>533116.02666197764</v>
+        <v>392773.75358548318</v>
       </c>
       <c r="E4" s="28">
         <f>+SIM②_月5投稿!J51</f>
-        <v>416994.30107700091</v>
+        <v>305760.52544897469</v>
       </c>
       <c r="F4" s="28"/>
     </row>
@@ -8869,11 +8862,11 @@
       </c>
       <c r="D5" s="28">
         <f>+SIM②_月5投稿!G61</f>
-        <v>883116.02666197764</v>
+        <v>692773.75358548318</v>
       </c>
       <c r="E5" s="28">
         <f>+SIM②_月5投稿!J61</f>
-        <v>766994.30107700091</v>
+        <v>605760.52544897469</v>
       </c>
       <c r="F5" s="27"/>
     </row>
@@ -8949,15 +8942,15 @@
       <c r="B10" s="7"/>
       <c r="C10" s="117">
         <f>+SIM②_月5投稿!D34</f>
-        <v>185057.66399999999</v>
+        <v>138793.24799999999</v>
       </c>
       <c r="D10" s="10">
         <f>+SIM②_月5投稿!G34</f>
-        <v>192705.34222065922</v>
+        <v>145924.58452849439</v>
       </c>
       <c r="E10" s="10">
         <f>+SIM②_月5投稿!J34</f>
-        <v>153998.10035900029</v>
+        <v>116920.17514965823</v>
       </c>
       <c r="F10" s="10"/>
     </row>
@@ -8968,15 +8961,15 @@
       <c r="B11" s="7"/>
       <c r="C11" s="117">
         <f>+SIM②_月5投稿!D35</f>
-        <v>5417.3780559359993</v>
+        <v>4063.0335419519997</v>
       </c>
       <c r="D11" s="10">
         <f>+SIM②_月5投稿!G35</f>
-        <v>45264.961655620551</v>
+        <v>34313.137652418496</v>
       </c>
       <c r="E11" s="10">
         <f>+SIM②_月5投稿!J35</f>
-        <v>36206.036827430449</v>
+        <v>27525.73895862071</v>
       </c>
       <c r="F11" s="10"/>
     </row>
@@ -8991,11 +8984,11 @@
       </c>
       <c r="D12" s="28">
         <f>+D4/D11</f>
-        <v>11.777675428468648</v>
+        <v>11.446745487520266</v>
       </c>
       <c r="E12" s="28">
         <f t="shared" ref="E12" si="0">+E4/E11</f>
-        <v>11.517258932937873</v>
+        <v>11.108167737426514</v>
       </c>
       <c r="F12" s="28"/>
     </row>
@@ -9010,11 +9003,11 @@
       </c>
       <c r="D13" s="28">
         <f>+D5/D11</f>
-        <v>19.509925433733823</v>
+        <v>20.189752409210364</v>
       </c>
       <c r="E13" s="28">
         <f t="shared" ref="E13" si="1">+E5/E11</f>
-        <v>21.184155137794868</v>
+        <v>22.007057698236952</v>
       </c>
       <c r="F13" s="28"/>
     </row>
@@ -9062,11 +9055,11 @@
       </c>
       <c r="D16" s="87">
         <f>+D17</f>
-        <v>249</v>
+        <v>192</v>
       </c>
       <c r="E16" s="87">
         <f>+E17</f>
-        <v>326</v>
+        <v>253</v>
       </c>
       <c r="F16" s="87"/>
       <c r="R16" s="5" t="s">
@@ -9090,11 +9083,11 @@
       </c>
       <c r="D17" s="87">
         <f>+SIM②_月5投稿!G36</f>
-        <v>249</v>
+        <v>192</v>
       </c>
       <c r="E17" s="87">
         <f>+SIM②_月5投稿!J36</f>
-        <v>326</v>
+        <v>253</v>
       </c>
       <c r="F17" s="10"/>
       <c r="R17" s="5">
@@ -9232,11 +9225,11 @@
       </c>
       <c r="D22" s="90">
         <f t="shared" ref="D22:E22" si="2">+IFERROR(D4/D16,"--")</f>
-        <v>2141.0282195260147</v>
+        <v>2045.6966332577249</v>
       </c>
       <c r="E22" s="90">
         <f t="shared" si="2"/>
-        <v>1279.1236229355857</v>
+        <v>1208.5396262805323</v>
       </c>
       <c r="F22" s="90"/>
       <c r="R22" s="34"/>
@@ -9256,11 +9249,11 @@
       </c>
       <c r="D23" s="90">
         <f t="shared" ref="D23" si="3">+IFERROR(D5/D16,"--")</f>
-        <v>3546.6507094858539</v>
+        <v>3608.1966332577249</v>
       </c>
       <c r="E23" s="90">
         <f t="shared" ref="E23" si="4">+IFERROR(E5/E16,"--")</f>
-        <v>2352.7432548374263</v>
+        <v>2394.3103772686745</v>
       </c>
       <c r="F23" s="90"/>
       <c r="R23" s="34"/>
@@ -9289,15 +9282,15 @@
       <c r="B25" s="7"/>
       <c r="C25" s="10">
         <f>+SIM②_月5投稿!E68+C29*C30</f>
-        <v>480172.99199999997</v>
+        <v>341379.74399999995</v>
       </c>
       <c r="D25" s="10">
         <f>+SIM②_月5投稿!G68+D29*D30</f>
-        <v>503116.02666197764</v>
+        <v>362773.75358548318</v>
       </c>
       <c r="E25" s="10">
         <f>+SIM②_月5投稿!J68+E29*E30</f>
-        <v>386994.30107700091</v>
+        <v>275760.52544897469</v>
       </c>
       <c r="F25" s="10"/>
       <c r="R25" s="34"/>
@@ -9333,15 +9326,15 @@
       </c>
       <c r="C29" s="5">
         <f>+IF(C10&lt;=30000,0,C10-30000)</f>
-        <v>155057.66399999999</v>
+        <v>108793.24799999999</v>
       </c>
       <c r="D29" s="91">
         <f>+IF(D10&lt;=30000,0,D10-30000)</f>
-        <v>162705.34222065922</v>
+        <v>115924.58452849439</v>
       </c>
       <c r="E29" s="91">
         <f>+IF(E10&lt;=30000,0,E10-30000)</f>
-        <v>123998.10035900029</v>
+        <v>86920.175149658229</v>
       </c>
       <c r="F29" s="91"/>
       <c r="R29" s="34"/>
@@ -9946,20 +9939,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="79deb97c-193b-473b-ac92-dc976e68b6a4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="79deb97c-193b-473b-ac92-dc976e68b6a4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9981,14 +9974,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CA9CD83-13A7-4B09-B9AB-AAF5EBC76B43}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{010C7DA8-EA1E-4EA4-BD5C-CCDDE9E9CCA3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -10002,4 +9987,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CA9CD83-13A7-4B09-B9AB-AAF5EBC76B43}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>